--- a/MSTELevel.xlsb.xlsx
+++ b/MSTELevel.xlsb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MathSaveTheEarth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9F8ECF-BD30-4704-973D-50F2D0E6BD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D625553-19F5-4EAE-8B8D-5CF5962D3770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>STAGE|1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,11 +108,63 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PRINT|"지금부터  ×가 등장합니다. ×을 활용해 더 강력한 수식을 만드세요!"|3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PRINT|"적의 대군단이 몰려옵니다!"|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRINT|"어떤 적은 정확한 숫자를 맞춰야  파괴할 수 있습니다."|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(6)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(12)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(18)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SYMBOL|+, ×, ×</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRINT|"소수는 +와 ×를 조합해서 만들 수 있습니다."|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(13)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(7)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(19)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(15)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(20)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NUMBER|1, 2, 3, 4, 5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRINT|"지금부터  ×가 등장합니다.\n×를 활용해 더 강력한 수식을 만드세요!"|4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -727,7 +780,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939BC4B4-D320-41F9-BACC-516C61336204}">
-  <dimension ref="A1:U70"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
@@ -750,282 +803,351 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E10" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C16" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E18" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C25" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D27" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E29" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G33" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F34" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E35" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D36" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C37" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E8" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C10" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E12" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C14" s="1">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>2</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" s="1">
+        <v>2</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B46" s="1">
+        <v>2</v>
+      </c>
+      <c r="D46" s="1">
+        <v>2</v>
+      </c>
+      <c r="F46" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>2</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2</v>
+      </c>
+      <c r="E47" s="1">
+        <v>2</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>3</v>
+      </c>
+      <c r="C49" s="1">
+        <v>3</v>
+      </c>
+      <c r="E49" s="1">
+        <v>3</v>
+      </c>
+      <c r="G49" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B50" s="1">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1">
+        <v>3</v>
+      </c>
+      <c r="F50" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>3</v>
+      </c>
+      <c r="C51" s="1">
+        <v>3</v>
+      </c>
+      <c r="E51" s="1">
+        <v>3</v>
+      </c>
+      <c r="G51" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>5</v>
+      </c>
+      <c r="C53" s="1">
+        <v>5</v>
+      </c>
+      <c r="E53" s="1">
+        <v>5</v>
+      </c>
+      <c r="G53" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B54" s="1">
+        <v>5</v>
+      </c>
+      <c r="D54" s="1">
+        <v>5</v>
+      </c>
+      <c r="F54" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>5</v>
+      </c>
+      <c r="C55" s="1">
+        <v>5</v>
+      </c>
+      <c r="E55" s="1">
+        <v>5</v>
+      </c>
+      <c r="G55" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>7</v>
+      </c>
+      <c r="C57" s="1">
+        <v>7</v>
+      </c>
+      <c r="E57" s="1">
+        <v>7</v>
+      </c>
+      <c r="G57" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B58" s="1">
+        <v>7</v>
+      </c>
+      <c r="D58" s="1">
+        <v>7</v>
+      </c>
+      <c r="F58" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>7</v>
+      </c>
+      <c r="C59" s="1">
+        <v>7</v>
+      </c>
+      <c r="E59" s="1">
+        <v>7</v>
+      </c>
+      <c r="G59" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B65" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E16" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="C18" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
-        <v>2</v>
-      </c>
-      <c r="C22" s="1">
-        <v>2</v>
-      </c>
-      <c r="E22" s="1">
-        <v>2</v>
-      </c>
-      <c r="G22" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B23" s="1">
-        <v>2</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="F23" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>2</v>
-      </c>
-      <c r="C24" s="1">
-        <v>2</v>
-      </c>
-      <c r="E24" s="1">
-        <v>2</v>
-      </c>
-      <c r="G24" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
-        <v>3</v>
-      </c>
-      <c r="C26" s="1">
-        <v>3</v>
-      </c>
-      <c r="E26" s="1">
-        <v>3</v>
-      </c>
-      <c r="G26" s="1">
-        <v>3</v>
-      </c>
-      <c r="R26" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B27" s="1">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1">
-        <v>3</v>
-      </c>
-      <c r="F27" s="1">
-        <v>3</v>
-      </c>
-      <c r="U27" s="1">
+      <c r="C65" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F65" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B66" s="1">
+        <v>10</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
-        <v>3</v>
-      </c>
-      <c r="C28" s="1">
-        <v>3</v>
-      </c>
-      <c r="E28" s="1">
-        <v>3</v>
-      </c>
-      <c r="G28" s="1">
-        <v>3</v>
-      </c>
-      <c r="O28" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="R29" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
-        <v>5</v>
-      </c>
-      <c r="C30" s="1">
-        <v>5</v>
-      </c>
-      <c r="E30" s="1">
-        <v>5</v>
-      </c>
-      <c r="G30" s="1">
-        <v>5</v>
-      </c>
-      <c r="U30" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B31" s="1">
-        <v>5</v>
-      </c>
-      <c r="D31" s="1">
-        <v>5</v>
-      </c>
-      <c r="F31" s="1">
-        <v>5</v>
-      </c>
-      <c r="O31" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
-        <v>5</v>
-      </c>
-      <c r="C32" s="1">
-        <v>5</v>
-      </c>
-      <c r="E32" s="1">
-        <v>5</v>
-      </c>
-      <c r="G32" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
-        <v>7</v>
-      </c>
-      <c r="C34" s="1">
-        <v>7</v>
-      </c>
-      <c r="E34" s="1">
-        <v>7</v>
-      </c>
-      <c r="G34" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="1">
-        <v>7</v>
-      </c>
-      <c r="D35" s="1">
-        <v>7</v>
-      </c>
-      <c r="F35" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
-        <v>7</v>
-      </c>
-      <c r="C36" s="1">
-        <v>7</v>
-      </c>
-      <c r="E36" s="1">
-        <v>7</v>
-      </c>
-      <c r="G36" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B56" s="1">
-        <v>6</v>
-      </c>
-      <c r="G56" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C57" s="1">
-        <v>6</v>
-      </c>
-      <c r="E57" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
-        <v>6</v>
-      </c>
-      <c r="G58" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C59" s="1">
-        <v>6</v>
-      </c>
-      <c r="F59" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
-        <v>12</v>
+      <c r="F66" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B67" s="1">
+        <v>10</v>
+      </c>
+      <c r="F67" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B68" s="1">
-        <v>10</v>
-      </c>
-      <c r="F68" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D69" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="1" t="s">
+      <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
     </row>
